--- a/output/pdf_financials_xlsx/ACT.xlsx
+++ b/output/pdf_financials_xlsx/ACT.xlsx
@@ -3921,10 +3921,10 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>0</v>
+        <v>-0.009996</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>-0.045554</v>
       </c>
       <c r="D124" s="1" t="inlineStr">
         <is>
@@ -3949,10 +3949,10 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>0</v>
+        <v>-0.009996</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>-0.045554</v>
       </c>
       <c r="D125" s="1" t="inlineStr">
         <is>
@@ -4917,7 +4917,11 @@
           <t>Finance lease repayments (Note 13)</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E16" s="5" t="n">
         <v>-0.009996</v>
       </c>

--- a/output/pdf_financials_xlsx/ACT.xlsx
+++ b/output/pdf_financials_xlsx/ACT.xlsx
@@ -3812,7 +3812,7 @@
         <v>0</v>
       </c>
       <c r="C120" s="3" t="n">
-        <v>0</v>
+        <v>2.162832</v>
       </c>
       <c r="D120" s="1" t="inlineStr">
         <is>
@@ -4712,7 +4712,11 @@
           <t>Issue of common shares, net of issuing costs</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>-</t>
